--- a/src/vlinder/data/refugee/xlsx/refugee.xlsx
+++ b/src/vlinder/data/refugee/xlsx/refugee.xlsx
@@ -1,31 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10811"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10414"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tdijk004/Documents/Tooling/tRBS/open source/trbs-refugee-2/trbs-add-refugee/model/data/refugee/xlsx/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ttami001/Documents/forked_tbrs_opensource/trbs/src/vlinder/data/refugee/xlsx/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E89EA71-60BF-0F4C-A7C6-D577FEDFF97E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE5C9004-8666-2D48-AEA8-D6E2D0FCD54D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="860" yWindow="2460" windowWidth="31660" windowHeight="15880" activeTab="5" xr2:uid="{4D223BC5-A265-7B41-9F5C-066E948A074C}"/>
+    <workbookView xWindow="860" yWindow="2460" windowWidth="31660" windowHeight="15880" activeTab="2" xr2:uid="{4D223BC5-A265-7B41-9F5C-066E948A074C}"/>
   </bookViews>
   <sheets>
     <sheet name="configurations" sheetId="1" r:id="rId1"/>
-    <sheet name="key_outputs" sheetId="2" r:id="rId2"/>
-    <sheet name="decision_makers_options" sheetId="3" r:id="rId3"/>
-    <sheet name="scenarios" sheetId="4" r:id="rId4"/>
-    <sheet name="fixed_inputs" sheetId="5" r:id="rId5"/>
-    <sheet name="dependencies" sheetId="6" r:id="rId6"/>
-    <sheet name="theme_weights" sheetId="7" r:id="rId7"/>
-    <sheet name="key_output_weights" sheetId="8" r:id="rId8"/>
-    <sheet name="scenario_weights" sheetId="9" r:id="rId9"/>
+    <sheet name="generic_text_elements" sheetId="10" r:id="rId2"/>
+    <sheet name="case_text_elements" sheetId="11" r:id="rId3"/>
+    <sheet name="key_outputs" sheetId="2" r:id="rId4"/>
+    <sheet name="decision_makers_options" sheetId="3" r:id="rId5"/>
+    <sheet name="scenarios" sheetId="4" r:id="rId6"/>
+    <sheet name="fixed_inputs" sheetId="5" r:id="rId7"/>
+    <sheet name="dependencies" sheetId="6" r:id="rId8"/>
+    <sheet name="theme_weights" sheetId="7" r:id="rId9"/>
+    <sheet name="key_output_weights" sheetId="8" r:id="rId10"/>
+    <sheet name="scenario_weights" sheetId="9" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">dependencies!$A$1:$H$98</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">fixed_inputs!$A$1:$B$46</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">dependencies!$A$1:$H$98</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">fixed_inputs!$A$1:$B$46</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -48,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="585" uniqueCount="204">
   <si>
     <t>configuration</t>
   </si>
@@ -582,13 +584,91 @@
   </si>
   <si>
     <t>-*</t>
+  </si>
+  <si>
+    <t>generic_text_element</t>
+  </si>
+  <si>
+    <t>title_strategic_challenge</t>
+  </si>
+  <si>
+    <t>Strategic Challenge</t>
+  </si>
+  <si>
+    <t>title_key_outputs</t>
+  </si>
+  <si>
+    <t>Key outputs</t>
+  </si>
+  <si>
+    <t>title_dmo</t>
+  </si>
+  <si>
+    <t>Options</t>
+  </si>
+  <si>
+    <t>title_scenarios</t>
+  </si>
+  <si>
+    <t>Scenarios</t>
+  </si>
+  <si>
+    <t>title_comparison</t>
+  </si>
+  <si>
+    <t>Comparisons of options</t>
+  </si>
+  <si>
+    <t>title_theme_weights</t>
+  </si>
+  <si>
+    <t>Key output and theme weights</t>
+  </si>
+  <si>
+    <t>title_scenario_weights</t>
+  </si>
+  <si>
+    <t>Scenario weights</t>
+  </si>
+  <si>
+    <t>text_strategic_challenge</t>
+  </si>
+  <si>
+    <t>Describing strategic challenge that requires a decision</t>
+  </si>
+  <si>
+    <t>text_key_outputs</t>
+  </si>
+  <si>
+    <t>Which indicators do you use to evaluate the impact of your decision(s)?</t>
+  </si>
+  <si>
+    <t>text_dmo</t>
+  </si>
+  <si>
+    <t>Which options do you have to influence your impact?</t>
+  </si>
+  <si>
+    <t>text_scenarios</t>
+  </si>
+  <si>
+    <t>Which uncertainty do you want to account for?</t>
+  </si>
+  <si>
+    <t>case_text_element</t>
+  </si>
+  <si>
+    <t>strategic_challenge</t>
+  </si>
+  <si>
+    <t>How to source energy?</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -601,6 +681,20 @@
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="5">
@@ -653,10 +747,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -664,10 +759,15 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Standaard" xfId="0" builtinId="0"/>
+  <cellStyles count="2">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{DA9729B0-9B76-C84C-86B6-0F66A13A4DF8}"/>
   </cellStyles>
   <dxfs count="1">
     <dxf>
@@ -694,9 +794,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Kantoorthema">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -734,7 +834,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -840,7 +940,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -982,7 +1082,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1017,7 +1117,271 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E33D2E0-445B-874F-A88A-006EF8EA7B4B}">
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="34.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82690612-F6E7-CC4A-A524-5770D0407DD2}">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>166</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0CE72EE-56C9-CF45-9BB4-E3A3014AFA69}">
+  <dimension ref="A1:B12"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="21.6640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="163.5" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="10.83203125" style="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A9" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A11" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A12" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>200</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2A4C952-3079-8241-9F47-5217040C7CD4}">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="18.1640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.83203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="10.83203125" style="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B3" s="7"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F27D205-AE79-E542-BA48-2D4707481E26}">
   <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -1242,7 +1606,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1DA06C9-587A-0249-BA81-B2630B23EDC5}">
   <dimension ref="A1:C26"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -1545,7 +1909,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9376F10E-70E0-5847-AA4E-1F18853CB3E7}">
   <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -1768,7 +2132,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED761DDB-51CF-394F-9D46-C056F7FA6C46}">
   <dimension ref="A1:B46"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -2153,7 +2517,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45498073-CC56-2D41-B5D6-3D03F1233978}">
   <dimension ref="A1:H98"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -3056,16 +3420,16 @@
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A61" s="5" t="s">
+      <c r="A61" t="s">
         <v>160</v>
       </c>
-      <c r="B61" s="5" t="s">
+      <c r="B61" t="s">
         <v>31</v>
       </c>
-      <c r="C61" s="5" t="s">
+      <c r="C61" t="s">
         <v>53</v>
       </c>
-      <c r="D61" s="5" t="s">
+      <c r="D61" t="s">
         <v>164</v>
       </c>
     </row>
@@ -3629,7 +3993,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E05F8AE-8DA8-724A-AD7F-0A10B8E741F3}">
   <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -3661,123 +4025,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E33D2E0-445B-874F-A88A-006EF8EA7B4B}">
-  <dimension ref="A1:B8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="34.33203125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>29</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>30</v>
-      </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>31</v>
-      </c>
-      <c r="B7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>32</v>
-      </c>
-      <c r="B8">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82690612-F6E7-CC4A-A524-5770D0407DD2}">
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>166</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>47</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>48</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>